--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>27.87</v>
+        <v>27.839</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1103,6 +1103,87 @@
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>D20260909M01</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>18200</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
@@ -1157,7 +1238,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1177,7 +1258,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1111,7 +1111,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>D20260909M01</t>
+          <t>D2026090901</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>33.86</v>
+        <v>34.4</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>18200</v>
+        <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -1184,6 +1184,87 @@
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>D20260909M01</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>18200</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
@@ -1238,7 +1319,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -1258,7 +1339,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>34.4</v>
+        <v>34.12</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>16700</v>
@@ -1217,54 +1217,216 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M02</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>长江电力(600900)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M03</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>美的集团(000333)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>85.86</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
@@ -1308,7 +1470,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1481,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -1339,7 +1501,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,11 +569,11 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -650,11 +650,11 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-4.38%</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.17%</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -731,11 +731,11 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-6.35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5.15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.78%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -569,11 +569,11 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-1.52%</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -650,11 +650,11 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-5.19%</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -731,11 +731,11 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-5.17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,54 +1379,297 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M04</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>美的集团(000333)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M05</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>长江电力(600900)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>D20260911M01</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>8700</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
@@ -1470,7 +1713,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1724,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -1491,7 +1734,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1511,7 +1754,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1522,7 +1765,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1777,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.38%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1432,6 +1432,249 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M04</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>美的集团(000333)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>D20260910M05</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>长江电力(600900)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>D20260911M01</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>8700</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1481,7 +1724,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -1501,7 +1744,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -573,24 +573,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>-1.17%</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
           <t>-1.21%</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>-1.21%</t>
-        </is>
-      </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -603,7 +603,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-4.38%</t>
+          <t>-3.39%</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-3.17%</t>
+          <t>-2.17%</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6.35%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-5.15%</t>
+          <t>-4.09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-2.78%</t>
+          <t>-2.07%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>-0.80%</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-3.39%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-2.17%</t>
+          <t>-2.44%</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-5.86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-4.09%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>-2.48%</t>
         </is>
       </c>
     </row>
